--- a/output/pdf_financials_xlsx/KGC.xlsx
+++ b/output/pdf_financials_xlsx/KGC.xlsx
@@ -1186,40 +1186,40 @@
         <v>-0.542328</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.569948</v>
+        <v>-2.569948</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6.980041</v>
+        <v>-6.980041</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.126399</v>
+        <v>-0.126399</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.609687</v>
+        <v>-0.609687</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.616957</v>
+        <v>-0.616957</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.720544</v>
+        <v>-0.720544</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.264176</v>
+        <v>-0.264176</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.168248</v>
+        <v>-0.168248</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.307606</v>
+        <v>-0.307606</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.459965</v>
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="17">
@@ -1454,40 +1454,40 @@
         <v>-0.542328</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.569948</v>
+        <v>-2.569948</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.980041</v>
+        <v>-6.980041</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.126399</v>
+        <v>-0.126399</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.609687</v>
+        <v>-0.609687</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.616957</v>
+        <v>-0.616957</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.720544</v>
+        <v>-0.720544</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.264176</v>
+        <v>-0.264176</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.168248</v>
+        <v>-0.168248</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.307606</v>
+        <v>-0.307606</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.459965</v>
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="21">
@@ -1610,40 +1610,40 @@
         <v>-0.542328</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.569948</v>
+        <v>-2.569948</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.980041</v>
+        <v>-6.980041</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.126399</v>
+        <v>-0.126399</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.609687</v>
+        <v>-0.609687</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.616957</v>
+        <v>-0.616957</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.720544</v>
+        <v>-0.720544</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.264176</v>
+        <v>-0.264176</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.168248</v>
+        <v>-0.168248</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.307606</v>
+        <v>-0.307606</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.459965</v>
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="24">
@@ -1766,10 +1766,10 @@
         <v>13.5582</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>25.69948</v>
+        <v>-25.69948</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>34.900205</v>
+        <v>-34.900205</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>30.48435</v>
+        <v>-30.48435</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1836,40 +1836,40 @@
         <v>-0.542328</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.569948</v>
+        <v>-2.569948</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.980041</v>
+        <v>-6.980041</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.126399</v>
+        <v>-0.126399</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.609687</v>
+        <v>-0.609687</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.616957</v>
+        <v>-0.616957</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.720544</v>
+        <v>-0.720544</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.264176</v>
+        <v>-0.264176</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.168248</v>
+        <v>-0.168248</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.307606</v>
+        <v>-0.307606</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.459965</v>
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="28">
@@ -1940,40 +1940,40 @@
         <v>-0.542328</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.569948</v>
+        <v>-2.569948</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.980041</v>
+        <v>-6.980041</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.126399</v>
+        <v>-0.126399</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.609687</v>
+        <v>-0.609687</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.616957</v>
+        <v>-0.616957</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.720544</v>
+        <v>-0.720544</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.264176</v>
+        <v>-0.264176</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.168248</v>
+        <v>-0.168248</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.307606</v>
+        <v>-0.307606</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.459965</v>
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="30">
@@ -2074,40 +2074,40 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5420,7 +5420,7 @@
         <v>1.239071</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.450731</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -10356,7 +10356,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -26755,16 +26759,16 @@
         </is>
       </c>
       <c r="P215" s="5" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="Q215" s="5" t="n">
-        <v>0.168248</v>
+        <v>-0.168248</v>
       </c>
       <c r="R215" s="5" t="n">
-        <v>0.307606</v>
+        <v>-0.307606</v>
       </c>
       <c r="S215" s="5" t="n">
-        <v>0.459965</v>
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="216">
@@ -27549,10 +27553,10 @@
         </is>
       </c>
       <c r="O224" s="5" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="P224" s="5" t="n">
-        <v>0.631696</v>
+        <v>-0.631696</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -27888,22 +27892,22 @@
         </is>
       </c>
       <c r="J228" s="5" t="n">
-        <v>0.126399</v>
+        <v>-0.126399</v>
       </c>
       <c r="K228" s="5" t="n">
-        <v>0.609687</v>
+        <v>-0.609687</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>0.616957</v>
+        <v>-0.616957</v>
       </c>
       <c r="M228" s="5" t="n">
-        <v>0.720544</v>
+        <v>-0.720544</v>
       </c>
       <c r="N228" s="5" t="n">
-        <v>0.264176</v>
+        <v>-0.264176</v>
       </c>
       <c r="O228" s="5" t="n">
-        <v>0.29035</v>
+        <v>-0.29035</v>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -30473,10 +30477,10 @@
         </is>
       </c>
       <c r="H257" s="5" t="n">
-        <v>2.569948</v>
+        <v>-2.569948</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>6.980041</v>
+        <v>-6.980041</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KGC.xlsx
+++ b/output/pdf_financials_xlsx/KGC.xlsx
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000705</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012062</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003801</v>
       </c>
     </row>
     <row r="13">
@@ -1863,13 +1863,13 @@
         <v>-0.631696</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.168248</v>
+        <v>-0.167543</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.307606</v>
+        <v>-0.295544</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.459965</v>
+        <v>-0.456164</v>
       </c>
     </row>
     <row r="28">
@@ -1967,13 +1967,13 @@
         <v>-0.631696</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.168248</v>
+        <v>-0.167543</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.307606</v>
+        <v>-0.295544</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.459965</v>
+        <v>-0.456164</v>
       </c>
     </row>
     <row r="30">
@@ -2224,19 +2224,19 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.204884</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.10884</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.09046</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.363217</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.177491</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.461003</v>
@@ -2328,19 +2328,19 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.204884</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.10884</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.09046</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.363217</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.177491</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.461003</v>
@@ -2952,19 +2952,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.204884</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.10884</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.09046</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.363217</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.179891</v>
+        <v>0.0024</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.00278</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">

--- a/output/pdf_financials_xlsx/KGC.xlsx
+++ b/output/pdf_financials_xlsx/KGC.xlsx
@@ -715,13 +715,13 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.096626</v>
+        <v>0.12876</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.578029</v>
+        <v>0.600029</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.634419</v>
+        <v>0.6576689999999999</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.029876</v>
@@ -923,10 +923,10 @@
         <v>-0.113363</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.542328</v>
+        <v>0.543625</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-2.201252</v>
+        <v>2.201252</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-1.951787</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>0.003144</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0.007993999999999999</v>
@@ -1659,7 +1659,7 @@
         <v>-0.06</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0.1</v>
@@ -1711,7 +1711,7 @@
         <v>-0.06</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0.1</v>
@@ -1763,7 +1763,7 @@
         <v>1.889383</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>13.5582</v>
+        <v>-13.5582</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>-25.69948</v>
@@ -4018,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01904</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0525</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001168</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.028385</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007132</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003306</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7409,7 +7409,7 @@
         <v>0.448511</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.412037</v>
+        <v>0.372037</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.365964</v>
@@ -7569,7 +7569,7 @@
         <v>0.412037</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.405964</v>
+        <v>0.365964</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>1.987332</v>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007132</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003306</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>-0.413232</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.05835</v>
+        <v>-1.065482</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.97422</v>
+        <v>-0.977526</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.002421</v>
@@ -7727,7 +7727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S271"/>
+  <dimension ref="A1:S282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13095,10 +13095,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G61" s="5" t="n">
+        <v>-0.001168</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>-0.028385</v>
@@ -17552,15 +17550,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="5" t="n">
+        <v>0.372037</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.365964</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -17639,15 +17633,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="5" t="n">
+        <v>0.365964</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>1.987332</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -21069,15 +21059,11 @@
       <c r="F151" s="5" t="n">
         <v>-0.036474</v>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>-0.006073</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>1.621368</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -23323,7 +23309,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -23427,10 +23417,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G177" s="5" t="n">
+        <v>-0.520945</v>
       </c>
       <c r="H177" s="5" t="n">
         <v>-2.237467</v>
@@ -24397,10 +24385,8 @@
       <c r="G188" s="5" t="n">
         <v>0.124005</v>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H188" s="5" t="n">
+        <v>1.007286</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -24557,28 +24543,32 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Items not affected by cash</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Interest receivable</t>
+          <t>Write-off of mineral property</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" s="5" t="n">
-        <v>-0.00082</v>
-      </c>
-      <c r="F190" s="5" t="n">
-        <v>0.000792</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>-0.001168</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>0.385048</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -24649,7 +24639,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Mineral property</t>
+          <t>Mineral properties</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -24666,10 +24656,8 @@
       <c r="G191" s="5" t="n">
         <v>-0.341181</v>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H191" s="5" t="n">
+        <v>-2.429406</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -24740,25 +24728,27 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Share subscriptions</t>
+          <t>Foreign exchange gain on cash held in foreign currency</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>0.2</v>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H192" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -24824,25 +24814,23 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Outflow of Cash and Cash Equivalents</t>
+          <t>Interest receivable</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E193" s="5" t="n">
+        <v>-0.00082</v>
       </c>
       <c r="F193" s="5" t="n">
-        <v>-0.036474</v>
+        <v>0.000792</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>-0.006073</v>
+        <v>-0.001168</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -24913,23 +24901,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents Consists of</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Term deposit</t>
+          <t>Mineral property</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" s="5" t="n">
-        <v>0.44385</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>0.411329</v>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.365731</v>
+        <v>-0.341181</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -25000,25 +24992,25 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2.    NATURE OF OPERATIONS AND GOING CONCERN</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>The Company was incorporated under the Business Corporations Act (Alberta) on April</t>
+          <t>Share subscriptions</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E195" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>0.002007</v>
-      </c>
-      <c r="G195" s="5" t="n">
-        <v>1.2e-05</v>
+        <v>0.2</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -25089,29 +25081,25 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Item not affected by cash</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E196" s="5" t="n">
-        <v>0.0275</v>
+          <t>Outflow of Cash and Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.036474</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>-0.006073</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -25182,25 +25170,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Item not affected by cash</t>
+          <t>Cash and Cash Equivalents Consists of</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Item not affected by cash total</t>
+          <t>Term deposit</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" s="5" t="n">
-        <v>-0.3393</v>
+        <v>0.44385</v>
       </c>
       <c r="F197" s="5" t="n">
-        <v>-0.113363</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.411329</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.365731</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -25271,25 +25257,25 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>2.    NATURE OF OPERATIONS AND GOING CONCERN</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Loan receivable</t>
+          <t>The Company was incorporated under the Business Corporations Act (Alberta) on April</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" s="5" t="n">
-        <v>-0.025814</v>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F198" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002007</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>1.2e-05</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -25360,21 +25346,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Supplemental Information</t>
+          <t>Item not affected by cash</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Interest paid $</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>InterestPaidSupplementalData</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="F199" s="5" t="n">
         <v>0</v>
@@ -25453,24 +25439,20 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Supplemental Information</t>
+          <t>Item not affected by cash</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Income taxes paid $</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
+          <t>Item not affected by cash total</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" s="5" t="n">
-        <v>0</v>
+        <v>-0.3393</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>0</v>
+        <v>-0.113363</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -25546,20 +25528,20 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1.    INCORPORATION AND NATURE OF OPERATIONS</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>([FKDQJH ³76;-9´ 3ROLF\ The Company became a reporting issuer on August</t>
+          <t>Loan receivable</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" s="5" t="n">
-        <v>0.002007</v>
+        <v>-0.025814</v>
       </c>
       <c r="F201" s="5" t="n">
-        <v>2.7e-05</v>
+        <v>0</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -25635,20 +25617,24 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1.    INCORPORATION AND NATURE OF OPERATIONS</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>of  listing on the TSX-V.  The Company has been granted an extension, by the TSX-V, to complete its QT until March</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Interest paid $</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E202" s="5" t="n">
-        <v>0.00201</v>
+        <v>0</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -25719,29 +25705,29 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Share-based compensation 7 $</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income taxes paid $</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -25798,43 +25784,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R203" s="5" t="n">
-        <v>0.074632</v>
-      </c>
-      <c r="S203" s="5" t="n">
-        <v>0.273</v>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>1.    INCORPORATION AND NATURE OF OPERATIONS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Management and consulting fees 7</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>([FKDQJH ³76;-9´ 3ROLF\ The Company became a reporting issuer on August</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="5" t="n">
+        <v>0.002007</v>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>2.7e-05</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -25891,39 +25873,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R204" s="5" t="n">
-        <v>0.105688</v>
-      </c>
-      <c r="S204" s="5" t="n">
-        <v>0.108458</v>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>1.    INCORPORATION AND NATURE OF OPERATIONS</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>of  listing on the TSX-V.  The Company has been granted an extension, by the TSX-V, to complete its QT until March</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" s="5" t="n">
-        <v>0.033335</v>
+        <v>0.00201</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>0.02835</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -25940,35 +25922,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J205" s="5" t="n">
-        <v>0.020892</v>
-      </c>
-      <c r="K205" s="5" t="n">
-        <v>0.090378</v>
-      </c>
-      <c r="L205" s="5" t="n">
-        <v>0.046473</v>
-      </c>
-      <c r="M205" s="5" t="n">
-        <v>0.011205</v>
-      </c>
-      <c r="N205" s="5" t="n">
-        <v>0.02573</v>
-      </c>
-      <c r="O205" s="5" t="n">
-        <v>0.041884</v>
-      </c>
-      <c r="P205" s="5" t="n">
-        <v>0.040616</v>
-      </c>
-      <c r="Q205" s="5" t="n">
-        <v>0.025974</v>
-      </c>
-      <c r="R205" s="5" t="n">
-        <v>0.030396</v>
-      </c>
-      <c r="S205" s="5" t="n">
-        <v>0.031616</v>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -25984,7 +25986,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Investor relations and website</t>
+          <t>Share-based compensation 7 $</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -26013,35 +26015,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J206" s="5" t="n">
-        <v>0.005196</v>
-      </c>
-      <c r="K206" s="5" t="n">
-        <v>0.099008</v>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v>0.079961</v>
-      </c>
-      <c r="M206" s="5" t="n">
-        <v>0.016411</v>
-      </c>
-      <c r="N206" s="5" t="n">
-        <v>0.015055</v>
-      </c>
-      <c r="O206" s="5" t="n">
-        <v>0.052745</v>
-      </c>
-      <c r="P206" s="5" t="n">
-        <v>0.025373</v>
-      </c>
-      <c r="Q206" s="5" t="n">
-        <v>0.029626</v>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R206" s="5" t="n">
-        <v>0.027706</v>
+        <v>0.074632</v>
       </c>
       <c r="S206" s="5" t="n">
-        <v>0.02693</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="207">
@@ -26057,58 +26075,84 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Management and consulting fees 7</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="n">
-        <v>0.016002</v>
-      </c>
-      <c r="F207" s="5" t="n">
-        <v>0.00735</v>
-      </c>
-      <c r="G207" s="5" t="n">
-        <v>0.029585</v>
-      </c>
-      <c r="H207" s="5" t="n">
-        <v>0.031846</v>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>0.01653</v>
-      </c>
-      <c r="J207" s="5" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="K207" s="5" t="n">
-        <v>0.017246</v>
-      </c>
-      <c r="L207" s="5" t="n">
-        <v>0.011722</v>
-      </c>
-      <c r="M207" s="5" t="n">
-        <v>0.01153</v>
-      </c>
-      <c r="N207" s="5" t="n">
-        <v>0.009389</v>
-      </c>
-      <c r="O207" s="5" t="n">
-        <v>0.009741</v>
-      </c>
-      <c r="P207" s="5" t="n">
-        <v>0.008003</v>
-      </c>
-      <c r="Q207" s="5" t="n">
-        <v>0.009724</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R207" s="5" t="n">
-        <v>0.015708</v>
+        <v>0.105688</v>
       </c>
       <c r="S207" s="5" t="n">
-        <v>0.013433</v>
+        <v>0.108458</v>
       </c>
     </row>
     <row r="208">
@@ -26124,23 +26168,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Office and administration</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>0.033335</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.02835</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -26158,34 +26198,34 @@
         </is>
       </c>
       <c r="J208" s="5" t="n">
-        <v>0.006072</v>
+        <v>0.020892</v>
       </c>
       <c r="K208" s="5" t="n">
-        <v>0.007076</v>
+        <v>0.090378</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>0.018299</v>
+        <v>0.046473</v>
       </c>
       <c r="M208" s="5" t="n">
-        <v>0.002406</v>
+        <v>0.011205</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>0.006894</v>
+        <v>0.02573</v>
       </c>
       <c r="O208" s="5" t="n">
-        <v>0.013948</v>
+        <v>0.041884</v>
       </c>
       <c r="P208" s="5" t="n">
-        <v>0.010591</v>
+        <v>0.040616</v>
       </c>
       <c r="Q208" s="5" t="n">
-        <v>0.008389000000000001</v>
+        <v>0.025974</v>
       </c>
       <c r="R208" s="5" t="n">
-        <v>0.010316</v>
+        <v>0.030396</v>
       </c>
       <c r="S208" s="5" t="n">
-        <v>0.007365</v>
+        <v>0.031616</v>
       </c>
     </row>
     <row r="209">
@@ -26201,14 +26241,10 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Investor relations and website</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -26219,44 +26255,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G209" s="5" t="n">
-        <v>0.052155</v>
-      </c>
-      <c r="H209" s="5" t="n">
-        <v>0.149297</v>
-      </c>
-      <c r="I209" s="5" t="n">
-        <v>0.126226</v>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J209" s="5" t="n">
-        <v>0.010886</v>
+        <v>0.005196</v>
       </c>
       <c r="K209" s="5" t="n">
-        <v>0.005553</v>
+        <v>0.099008</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>0.004735</v>
+        <v>0.079961</v>
       </c>
       <c r="M209" s="5" t="n">
-        <v>0.001459</v>
+        <v>0.016411</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>0.001149</v>
+        <v>0.015055</v>
       </c>
       <c r="O209" s="5" t="n">
-        <v>0.003582</v>
+        <v>0.052745</v>
       </c>
       <c r="P209" s="5" t="n">
-        <v>0.002226</v>
+        <v>0.025373</v>
       </c>
       <c r="Q209" s="5" t="n">
-        <v>0.002507</v>
+        <v>0.029626</v>
       </c>
       <c r="R209" s="5" t="n">
-        <v>0.001602</v>
+        <v>0.027706</v>
       </c>
       <c r="S209" s="5" t="n">
-        <v>0.001367</v>
+        <v>0.02693</v>
       </c>
     </row>
     <row r="210">
@@ -26272,74 +26314,58 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>0.016002</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>0.00735</v>
+      </c>
+      <c r="G210" s="5" t="n">
+        <v>0.029585</v>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.010876</v>
+        <v>0.031846</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>0.011365</v>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01653</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>0.017246</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>0.011722</v>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>0.01153</v>
+      </c>
+      <c r="N210" s="5" t="n">
+        <v>0.009389</v>
       </c>
       <c r="O210" s="5" t="n">
-        <v>0.00585</v>
+        <v>0.009741</v>
       </c>
       <c r="P210" s="5" t="n">
-        <v>0.009108</v>
+        <v>0.008003</v>
       </c>
       <c r="Q210" s="5" t="n">
-        <v>0.00808</v>
+        <v>0.009724</v>
       </c>
       <c r="R210" s="5" t="n">
-        <v>0.00595</v>
+        <v>0.015708</v>
       </c>
       <c r="S210" s="5" t="n">
-        <v>0.001307</v>
+        <v>0.013433</v>
       </c>
     </row>
     <row r="211">
@@ -26355,10 +26381,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Office and administration</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -26384,53 +26414,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J211" s="5" t="n">
+        <v>0.006072</v>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>0.007076</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>0.018299</v>
+      </c>
+      <c r="M211" s="5" t="n">
+        <v>0.002406</v>
+      </c>
+      <c r="N211" s="5" t="n">
+        <v>0.006894</v>
+      </c>
+      <c r="O211" s="5" t="n">
+        <v>0.013948</v>
+      </c>
+      <c r="P211" s="5" t="n">
+        <v>0.010591</v>
+      </c>
+      <c r="Q211" s="5" t="n">
+        <v>0.008389000000000001</v>
+      </c>
+      <c r="R211" s="5" t="n">
+        <v>0.010316</v>
       </c>
       <c r="S211" s="5" t="n">
-        <v>0.00029</v>
+        <v>0.007365</v>
       </c>
     </row>
     <row r="212">
@@ -26446,60 +26458,62 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Travel and promotion</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="n">
-        <v>0.3668</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>0.113363</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>0.542328</v>
+        <v>0.052155</v>
       </c>
       <c r="H212" s="5" t="n">
-        <v>2.201252</v>
+        <v>0.149297</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>1.951787</v>
+        <v>0.126226</v>
       </c>
       <c r="J212" s="5" t="n">
-        <v>0.126399</v>
+        <v>0.010886</v>
       </c>
       <c r="K212" s="5" t="n">
-        <v>0.605678</v>
+        <v>0.005553</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>0.321145</v>
+        <v>0.004735</v>
       </c>
       <c r="M212" s="5" t="n">
-        <v>0.104519</v>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001459</v>
+      </c>
+      <c r="N212" s="5" t="n">
+        <v>0.001149</v>
       </c>
       <c r="O212" s="5" t="n">
-        <v>0.29035</v>
+        <v>0.003582</v>
       </c>
       <c r="P212" s="5" t="n">
-        <v>0.240872</v>
+        <v>0.002226</v>
       </c>
       <c r="Q212" s="5" t="n">
-        <v>0.168953</v>
+        <v>0.002507</v>
       </c>
       <c r="R212" s="5" t="n">
-        <v>0.271998</v>
+        <v>0.001602</v>
       </c>
       <c r="S212" s="5" t="n">
-        <v>0.463766</v>
+        <v>0.001367</v>
       </c>
     </row>
     <row r="213">
@@ -26510,17 +26524,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -26538,15 +26552,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>0.010876</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>0.011365</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -26573,24 +26583,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O213" s="5" t="n">
+        <v>0.00585</v>
+      </c>
+      <c r="P213" s="5" t="n">
+        <v>0.009108</v>
       </c>
       <c r="Q213" s="5" t="n">
-        <v>-0.000705</v>
+        <v>0.00808</v>
       </c>
       <c r="R213" s="5" t="n">
-        <v>-0.012062</v>
+        <v>0.00595</v>
       </c>
       <c r="S213" s="5" t="n">
-        <v>-0.003801</v>
+        <v>0.001307</v>
       </c>
     </row>
     <row r="214">
@@ -26601,12 +26607,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5</t>
+          <t>Meals and entertainment</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -26665,21 +26671,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P214" s="5" t="n">
-        <v>0.390824</v>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R214" s="5" t="n">
-        <v>0.04767</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S214" s="5" t="n">
+        <v>0.00029</v>
       </c>
     </row>
     <row r="215">
@@ -26690,85 +26698,65 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>0.113363</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>0.542328</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>2.201252</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>1.951787</v>
+      </c>
+      <c r="J215" s="5" t="n">
+        <v>0.126399</v>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>0.605678</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>0.321145</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>0.104519</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O215" s="5" t="n">
+        <v>0.29035</v>
       </c>
       <c r="P215" s="5" t="n">
-        <v>-0.631696</v>
+        <v>0.240872</v>
       </c>
       <c r="Q215" s="5" t="n">
-        <v>-0.168248</v>
+        <v>0.168953</v>
       </c>
       <c r="R215" s="5" t="n">
-        <v>-0.307606</v>
+        <v>0.271998</v>
       </c>
       <c r="S215" s="5" t="n">
-        <v>-0.459965</v>
+        <v>0.463766</v>
       </c>
     </row>
     <row r="216">
@@ -26784,12 +26772,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Basic and Diluted Loss per Share $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -26807,11 +26795,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" s="5" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="I216" s="5" t="n">
-        <v>2e-07</v>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -26843,17 +26835,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P216" s="5" t="n">
-        <v>6e-09</v>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q216" s="5" t="n">
-        <v>2e-09</v>
+        <v>-0.000705</v>
       </c>
       <c r="R216" s="5" t="n">
-        <v>3e-09</v>
+        <v>-0.012062</v>
       </c>
       <c r="S216" s="5" t="n">
-        <v>4e-09</v>
+        <v>-0.003801</v>
       </c>
     </row>
     <row r="217">
@@ -26869,7 +26863,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Weighted Average Common Shares</t>
+          <t>Impairment of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -26929,16 +26923,20 @@
         </is>
       </c>
       <c r="P217" s="5" t="n">
-        <v>100.977659</v>
-      </c>
-      <c r="Q217" s="5" t="n">
-        <v>102.527213</v>
+        <v>0.390824</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R217" s="5" t="n">
-        <v>103.991075</v>
-      </c>
-      <c r="S217" s="5" t="n">
-        <v>106.799702</v>
+        <v>0.04767</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -26949,17 +26947,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Management and consulting fees 7 $</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -26997,11 +26995,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L218" s="5" t="n">
-        <v>0.1589</v>
-      </c>
-      <c r="M218" s="5" t="n">
-        <v>0.06115</v>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -27014,18 +27016,16 @@
         </is>
       </c>
       <c r="P218" s="5" t="n">
-        <v>0.144955</v>
+        <v>-0.631696</v>
       </c>
       <c r="Q218" s="5" t="n">
-        <v>0.08465300000000001</v>
+        <v>-0.168248</v>
       </c>
       <c r="R218" s="5" t="n">
-        <v>0.105688</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.307606</v>
+      </c>
+      <c r="S218" s="5" t="n">
+        <v>-0.459965</v>
       </c>
     </row>
     <row r="219">
@@ -27036,15 +27036,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Share-based compensation 7</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Basic and Diluted Loss per Share $</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -27055,20 +27059,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G219" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="H219" s="5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="I219" s="5" t="n">
+        <v>2e-07</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -27100,23 +27098,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P219" s="5" t="n">
+        <v>6e-09</v>
+      </c>
+      <c r="Q219" s="5" t="n">
+        <v>2e-09</v>
       </c>
       <c r="R219" s="5" t="n">
-        <v>0.074632</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-09</v>
+      </c>
+      <c r="S219" s="5" t="n">
+        <v>4e-09</v>
       </c>
     </row>
     <row r="220">
@@ -27132,7 +27124,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Other Items total</t>
+          <t>Weighted Average Common Shares</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -27192,20 +27184,16 @@
         </is>
       </c>
       <c r="P220" s="5" t="n">
-        <v>0.390824</v>
+        <v>100.977659</v>
       </c>
       <c r="Q220" s="5" t="n">
-        <v>-0.000705</v>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>102.527213</v>
+      </c>
+      <c r="R220" s="5" t="n">
+        <v>103.991075</v>
+      </c>
+      <c r="S220" s="5" t="n">
+        <v>106.799702</v>
       </c>
     </row>
     <row r="221">
@@ -27221,7 +27209,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Management and consulting fees 6 $</t>
+          <t>Management and consulting fees 7 $</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -27264,34 +27252,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v>0.053483</v>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v>0.129228</v>
+      <c r="L221" s="5" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="M221" s="5" t="n">
+        <v>0.06115</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P221" s="5" t="n">
         <v>0.144955</v>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q221" s="5" t="n">
+        <v>0.08465300000000001</v>
+      </c>
+      <c r="R221" s="5" t="n">
+        <v>0.105688</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -27312,7 +27296,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Share-based payments 5</t>
+          <t>Share-based compensation 7</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -27366,8 +27350,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O222" s="5" t="n">
-        <v>0.033372</v>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
@@ -27379,10 +27365,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R222" s="5" t="n">
+        <v>0.074632</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -27398,12 +27382,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 4</t>
+          <t>Other Items total</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -27465,10 +27449,8 @@
       <c r="P223" s="5" t="n">
         <v>0.390824</v>
       </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q223" s="5" t="n">
+        <v>-0.000705</v>
       </c>
       <c r="R223" t="inlineStr">
         <is>
@@ -27489,17 +27471,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
+          <t>Management and consulting fees 6 $</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -27547,16 +27529,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N224" s="5" t="n">
+        <v>0.053483</v>
       </c>
       <c r="O224" s="5" t="n">
-        <v>-0.29035</v>
+        <v>0.129228</v>
       </c>
       <c r="P224" s="5" t="n">
-        <v>-0.631696</v>
+        <v>0.144955</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -27582,19 +27562,15 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Basic and Diluted Loss per Share $</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based payments 5</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -27646,10 +27622,12 @@
         </is>
       </c>
       <c r="O225" s="5" t="n">
-        <v>3e-09</v>
-      </c>
-      <c r="P225" s="5" t="n">
-        <v>6e-09</v>
+        <v>0.033372</v>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -27680,7 +27658,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Weighted Average Common Shares</t>
+          <t>Impairment of exploration and evaluation assets 4</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -27734,11 +27712,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O226" s="5" t="n">
-        <v>90.212778</v>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P226" s="5" t="n">
-        <v>100.977569</v>
+        <v>0.390824</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -27764,15 +27744,19 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Share-based payments 5,6</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -27818,16 +27802,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N227" s="5" t="n">
-        <v>0.152476</v>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O227" s="5" t="n">
-        <v>0.033372</v>
-      </c>
-      <c r="P227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.29035</v>
+      </c>
+      <c r="P227" s="5" t="n">
+        <v>-0.631696</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -27853,17 +27837,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year $</t>
+          <t>Basic and Diluted Loss per Share $</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -27891,28 +27875,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J228" s="5" t="n">
-        <v>-0.126399</v>
-      </c>
-      <c r="K228" s="5" t="n">
-        <v>-0.609687</v>
-      </c>
-      <c r="L228" s="5" t="n">
-        <v>-0.616957</v>
-      </c>
-      <c r="M228" s="5" t="n">
-        <v>-0.720544</v>
-      </c>
-      <c r="N228" s="5" t="n">
-        <v>-0.264176</v>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O228" s="5" t="n">
-        <v>-0.29035</v>
-      </c>
-      <c r="P228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-09</v>
+      </c>
+      <c r="P228" s="5" t="n">
+        <v>6e-09</v>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
@@ -27938,27 +27930,29 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Basic and Diluted Loss per Share $</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E229" s="5" t="n">
-        <v>-2.6e-07</v>
-      </c>
-      <c r="F229" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="G229" s="5" t="n">
-        <v>-4e-08</v>
+          <t>Weighted Average Common Shares</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -27970,28 +27964,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J229" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="K229" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-      <c r="L229" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="M229" s="5" t="n">
-        <v>1e-08</v>
-      </c>
-      <c r="N229" s="5" t="n">
-        <v>4e-09</v>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O229" s="5" t="n">
-        <v>3e-09</v>
-      </c>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.212778</v>
+      </c>
+      <c r="P229" s="5" t="n">
+        <v>100.977569</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -28022,7 +28024,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Weighted Average Common Shares</t>
+          <t>Share-based payments 5,6</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -28072,10 +28074,10 @@
         </is>
       </c>
       <c r="N230" s="5" t="n">
-        <v>68.231285</v>
+        <v>0.152476</v>
       </c>
       <c r="O230" s="5" t="n">
-        <v>90.212778</v>
+        <v>0.033372</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -28111,12 +28113,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -28129,36 +28131,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G231" s="5" t="n">
-        <v>0.000762</v>
-      </c>
-      <c r="H231" s="5" t="n">
-        <v>0.013065</v>
-      </c>
-      <c r="I231" s="5" t="n">
-        <v>0.009518</v>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J231" s="5" t="n">
-        <v>0.000704</v>
+        <v>-0.126399</v>
       </c>
       <c r="K231" s="5" t="n">
-        <v>0.001393</v>
+        <v>-0.609687</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>0.001055</v>
+        <v>-0.616957</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>0.000358</v>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.720544</v>
+      </c>
+      <c r="N231" s="5" t="n">
+        <v>-0.264176</v>
+      </c>
+      <c r="O231" s="5" t="n">
+        <v>-0.29035</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -28194,24 +28198,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic and Diluted Loss per Share $</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>-2.6e-07</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -28223,31 +28225,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J232" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>2e-08</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>0.317312</v>
+        <v>1e-08</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.616025</v>
-      </c>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-08</v>
+      </c>
+      <c r="N232" s="5" t="n">
+        <v>4e-09</v>
+      </c>
+      <c r="O232" s="5" t="n">
+        <v>3e-09</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -28283,7 +28277,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>Weighted Average Common Shares</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -28322,23 +28316,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L233" s="5" t="n">
-        <v>-0.0215</v>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N233" s="5" t="n">
+        <v>68.231285</v>
+      </c>
+      <c r="O233" s="5" t="n">
+        <v>90.212778</v>
       </c>
       <c r="P233" t="inlineStr">
         <is>
@@ -28369,41 +28361,49 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Common Shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Outstanding</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" s="5" t="n">
-        <v>1.433675</v>
-      </c>
-      <c r="F234" s="5" t="n">
-        <v>1.816667</v>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>12.841232</v>
+        <v>0.000762</v>
       </c>
       <c r="H234" s="5" t="n">
-        <v>26.391134</v>
+        <v>0.013065</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>34.452177</v>
+        <v>0.009518</v>
       </c>
       <c r="J234" s="5" t="n">
-        <v>14.815842</v>
+        <v>0.000704</v>
       </c>
       <c r="K234" s="5" t="n">
-        <v>32.013437</v>
+        <v>0.001393</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>57.62866</v>
+        <v>0.001055</v>
       </c>
       <c r="M234" s="5" t="n">
-        <v>61.70277</v>
+        <v>0.000358</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Share-based payments 7, 8 $</t>
+          <t>Impairment of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -28483,18 +28483,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K235" s="5" t="n">
-        <v>0.252758</v>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>0.317312</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>0.616025</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -28540,14 +28538,10 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Management and consulting fees 8</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -28573,16 +28567,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J236" s="5" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="K236" s="5" t="n">
-        <v>0.11285</v>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -28628,55 +28624,41 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted Average Number of Common Shares</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Accretion of convertible debentures and interest 6</t>
+          <t>Outstanding</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E237" s="5" t="n">
+        <v>1.433675</v>
+      </c>
+      <c r="F237" s="5" t="n">
+        <v>1.816667</v>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>12.841232</v>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>26.391134</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>34.452177</v>
       </c>
       <c r="J237" s="5" t="n">
-        <v>0.053149</v>
+        <v>14.815842</v>
       </c>
       <c r="K237" s="5" t="n">
-        <v>0.019506</v>
-      </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.013437</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>57.62866</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>61.70277</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -28722,7 +28704,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Loss on settlement of accounts payable 7</t>
+          <t>Share-based payments 7, 8 $</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -28757,7 +28739,7 @@
         </is>
       </c>
       <c r="K238" s="5" t="n">
-        <v>0.011675</v>
+        <v>0.252758</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -28813,10 +28795,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Gain on settlement of convertible debentures 6, 7</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Management and consulting fees 8</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -28842,13 +28828,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J239" s="5" t="n">
+        <v>0.0231</v>
       </c>
       <c r="K239" s="5" t="n">
-        <v>-0.007756</v>
+        <v>0.11285</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -28904,14 +28888,10 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Consulting fees (note 10) $</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accretion of convertible debentures and interest 6</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -28927,21 +28907,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H240" s="5" t="n">
-        <v>0.269121</v>
-      </c>
-      <c r="I240" s="5" t="n">
-        <v>0.406598</v>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" s="5" t="n">
+        <v>0.053149</v>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>0.019506</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -28997,14 +28977,10 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Professional fees (note 10)</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Loss on settlement of accounts payable 7</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -29020,21 +28996,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="5" t="n">
-        <v>0.289747</v>
-      </c>
-      <c r="I241" s="5" t="n">
-        <v>0.38899</v>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K241" s="5" t="n">
+        <v>0.011675</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -29090,7 +29068,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Share-based payments (notes 9(d) and 10)</t>
+          <t>Gain on settlement of convertible debentures 6, 7</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -29109,21 +29087,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="5" t="n">
-        <v>1.007286</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>0.271924</v>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K242" s="5" t="n">
+        <v>-0.007756</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -29179,7 +29159,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Office, rent and administration (note 10)</t>
+          <t>Consulting fees (note 10) $</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29203,10 +29183,10 @@
         </is>
       </c>
       <c r="H243" s="5" t="n">
-        <v>0.143532</v>
+        <v>0.269121</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>0.171583</v>
+        <v>0.406598</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -29272,12 +29252,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Professional fees (note 10)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -29296,10 +29276,10 @@
         </is>
       </c>
       <c r="H244" s="5" t="n">
-        <v>0.007993999999999999</v>
+        <v>0.289747</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>0.18344</v>
+        <v>0.38899</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -29365,7 +29345,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Business investigation costs</t>
+          <t>Share-based payments (notes 9(d) and 10)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -29385,10 +29365,10 @@
         </is>
       </c>
       <c r="H245" s="5" t="n">
-        <v>0.059514</v>
+        <v>1.007286</v>
       </c>
       <c r="I245" s="5" t="n">
-        <v>0.113033</v>
+        <v>0.271924</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -29454,10 +29434,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Wages</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Office, rent and administration (note 10)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -29474,10 +29458,10 @@
         </is>
       </c>
       <c r="H246" s="5" t="n">
-        <v>0.045591</v>
+        <v>0.143532</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>0.107949</v>
+        <v>0.171583</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -29543,10 +29527,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -29557,18 +29545,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G247" s="5" t="n">
+        <v>0.003144</v>
+      </c>
+      <c r="H247" s="5" t="n">
+        <v>0.007993999999999999</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>0.06583700000000001</v>
+        <v>0.18344</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -29634,14 +29618,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Transfer agent fees, press releases and investor relations</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Business investigation costs</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -29658,10 +29638,10 @@
         </is>
       </c>
       <c r="H248" s="5" t="n">
-        <v>0.141435</v>
+        <v>0.059514</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>0.035355</v>
+        <v>0.113033</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -29727,7 +29707,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Directors’ fees</t>
+          <t>Wages</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -29747,10 +29727,10 @@
         </is>
       </c>
       <c r="H249" s="5" t="n">
-        <v>0.022</v>
+        <v>0.045591</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>0.02325</v>
+        <v>0.107949</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -29816,7 +29796,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -29841,7 +29821,7 @@
         </is>
       </c>
       <c r="I250" s="5" t="n">
-        <v>0.009842</v>
+        <v>0.06583700000000001</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -29907,12 +29887,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Transfer agent fees, press releases and investor relations</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -29925,16 +29905,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G251" s="5" t="n">
+        <v>0.032134</v>
       </c>
       <c r="H251" s="5" t="n">
-        <v>0.006278</v>
+        <v>0.141435</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>0.008376</v>
+        <v>0.035355</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -30000,10 +29978,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Professional development</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Directors’ fees</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -30020,10 +30002,10 @@
         </is>
       </c>
       <c r="H252" s="5" t="n">
-        <v>0.00367</v>
+        <v>0.022</v>
       </c>
       <c r="I252" s="5" t="n">
-        <v>0.001971</v>
+        <v>0.02325</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -30084,12 +30066,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (note 7)</t>
+          <t>Subcontractors</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -30108,11 +30090,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H253" s="5" t="n">
-        <v>0.385048</v>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I253" s="5" t="n">
-        <v>5.03094</v>
+        <v>0.009842</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -30173,15 +30157,19 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Write-off of equipment</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -30197,13 +30185,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H254" s="5" t="n">
+        <v>0.006278</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>0.008533000000000001</v>
+        <v>0.008376</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -30264,12 +30250,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Other Items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Interest earned</t>
+          <t>Professional development</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -30289,12 +30275,10 @@
         </is>
       </c>
       <c r="H255" s="5" t="n">
-        <v>-0.016352</v>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00367</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>0.001971</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -30360,7 +30344,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment (11,219)</t>
+          <t>Write-off of exploration and evaluation assets (note 7)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -30379,15 +30363,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H256" s="5" t="n">
+        <v>0.385048</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>5.03094</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -30453,14 +30433,10 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for Year $</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of equipment</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -30476,11 +30452,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H257" s="5" t="n">
-        <v>-2.569948</v>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I257" s="5" t="n">
-        <v>-6.980041</v>
+        <v>0.008533000000000001</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -30541,12 +30519,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 9(d)) $</t>
+          <t>Interest earned</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -30561,12 +30539,10 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>0.124005</v>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001297</v>
+      </c>
+      <c r="H258" s="5" t="n">
+        <v>-0.016352</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -30632,12 +30608,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Business investigation costs (note 11)</t>
+          <t>Gain on disposal of equipment (11,219)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -30646,11 +30622,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F259" s="5" t="n">
-        <v>0.074545</v>
-      </c>
-      <c r="G259" s="5" t="n">
-        <v>0.113366</v>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -30721,17 +30701,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Professional fees (note 11)</t>
+          <t>Net Loss and Comprehensive Loss for Year $</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -30739,21 +30719,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F260" s="5" t="n">
-        <v>0.02835</v>
-      </c>
-      <c r="G260" s="5" t="n">
-        <v>0.06679599999999999</v>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>-2.569948</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>-6.980041</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -30819,14 +30799,10 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Consulting fees (note 11)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (note 9(d)) $</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -30838,12 +30814,10 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.124005</v>
+      </c>
+      <c r="H261" s="5" t="n">
+        <v>1.007286</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -30914,12 +30888,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Office, rent and administration (note 11)</t>
+          <t>Professional fees (note 11)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -30927,18 +30901,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F262" s="5" t="n">
+        <v>0.02835</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>0.033864</v>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06679599999999999</v>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>0.289747</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -31009,23 +30979,29 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Transfer agent fees and press releases</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" s="5" t="n">
-        <v>0.010454</v>
-      </c>
-      <c r="F263" s="5" t="n">
-        <v>0.005289</v>
+          <t>Consulting fees (note 11)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>0.032134</v>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.062</v>
+      </c>
+      <c r="H263" s="5" t="n">
+        <v>0.269121</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -31096,10 +31072,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bad debts (note 6)</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Office, rent and administration (note 11)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -31111,12 +31091,10 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>0.025814</v>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033864</v>
+      </c>
+      <c r="H264" s="5" t="n">
+        <v>0.143432</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -31187,31 +31165,23 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Business investigation costs (note 11)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F265" s="5" t="n">
+        <v>0.074545</v>
       </c>
       <c r="G265" s="5" t="n">
-        <v>0.003144</v>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.113366</v>
+      </c>
+      <c r="H265" s="5" t="n">
+        <v>0.059514</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -31282,23 +31252,27 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Interest earned</t>
+          <t>Wages (note 11)</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" s="5" t="n">
-        <v>-0.012698</v>
-      </c>
-      <c r="F266" s="5" t="n">
-        <v>-0.002171</v>
-      </c>
-      <c r="G266" s="5" t="n">
-        <v>-0.001297</v>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="n">
+        <v>0.045591</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -31369,27 +31343,27 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss for the Year</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E267" s="5" t="n">
-        <v>-0.3668</v>
-      </c>
-      <c r="F267" s="5" t="n">
-        <v>-0.113363</v>
-      </c>
-      <c r="G267" s="5" t="n">
-        <v>-0.542328</v>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>'LUHFWRUV¶ IHHV (note 11)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>0.022</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -31460,18 +31434,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Deficit, Beginning of Year</t>
+          <t>Bad debts</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
-      <c r="E268" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>-0.3668</v>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>-0.480163</v>
+        <v>0.025814</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -31547,23 +31525,29 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Deficit, End of Year $</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" s="5" t="n">
-        <v>-0.3668</v>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>-0.480163</v>
+          <t>Loss Before Other Items</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>-1.022491</v>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.543625</v>
+      </c>
+      <c r="H269" s="5" t="n">
+        <v>2.201252</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -31629,30 +31613,32 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Items</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Business investigation costs $</t>
+          <t>Write-off of mineral property (note 8(e))</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" s="5" t="n">
-        <v>0.292207</v>
-      </c>
-      <c r="F270" s="5" t="n">
-        <v>0.074545</v>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H270" s="5" t="n">
+        <v>0.385048</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -31718,82 +31704,1067 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="n">
+        <v>-0.542328</v>
+      </c>
+      <c r="H271" s="5" t="n">
+        <v>-2.569948</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Deficit, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="n">
+        <v>0.480163</v>
+      </c>
+      <c r="H272" s="5" t="n">
+        <v>1.022491</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Deficit, End of Year $</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>1.022491</v>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>3.592439</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Transfer agent fees and press releases</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" s="5" t="n">
+        <v>0.010454</v>
+      </c>
+      <c r="F274" s="5" t="n">
+        <v>0.005289</v>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>0.032134</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Bad debts (note 6)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="n">
+        <v>0.025814</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="n">
+        <v>0.003144</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Interest earned</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" s="5" t="n">
+        <v>-0.012698</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>-0.002171</v>
+      </c>
+      <c r="G277" s="5" t="n">
+        <v>-0.001297</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the Year</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>-0.3668</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>-0.113363</v>
+      </c>
+      <c r="G278" s="5" t="n">
+        <v>-0.542328</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Deficit, Beginning of Year</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="5" t="n">
+        <v>-0.3668</v>
+      </c>
+      <c r="G279" s="5" t="n">
+        <v>-0.480163</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Deficit, End of Year $</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" s="5" t="n">
+        <v>-0.3668</v>
+      </c>
+      <c r="F280" s="5" t="n">
+        <v>-0.480163</v>
+      </c>
+      <c r="G280" s="5" t="n">
+        <v>-1.022491</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Business investigation costs $</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" s="5" t="n">
+        <v>0.292207</v>
+      </c>
+      <c r="F281" s="5" t="n">
+        <v>0.074545</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
         <is>
           <t>Stock-based compensation</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" s="5" t="n">
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" s="5" t="n">
         <v>0.0275</v>
       </c>
-      <c r="F271" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S271" t="inlineStr">
+      <c r="F282" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
         <is>
           <t>-</t>
         </is>
